--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136621778</v>
       </c>
       <c r="B4" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>136622764</v>
       </c>
       <c r="B5" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136621778</v>
       </c>
       <c r="B4" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>136622764</v>
       </c>
       <c r="B5" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136621778</v>
       </c>
       <c r="B4" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>136622764</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136621778</v>
       </c>
       <c r="B4" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>136622764</v>
       </c>
       <c r="B5" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,48 +918,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136621778</v>
+        <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>98215</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högalund_, Högalund_, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496834</v>
+        <v>496599</v>
       </c>
       <c r="R4" t="n">
-        <v>6493630</v>
+        <v>6493658</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +987,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>8 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,54 +1033,58 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621778</t>
+          <t>https://artportalen.se/Sighting/136888547</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136622764</v>
+        <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>98218</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högalund_, Högalund_, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496794</v>
+        <v>496617</v>
       </c>
       <c r="R5" t="n">
-        <v>6493655</v>
+        <v>6493668</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1108,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>58 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1154,707 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136889141</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136889997</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högalund_, Högalund_, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>496656</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6493647</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>21 ex</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136889997</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136890779</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högalund_, Högalund_, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496603</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6493653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>11 ex</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890779</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136621778</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högalund_, Högalund_, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496834</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6493630</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621778</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136622764</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98218</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högalund_, Högalund_, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496794</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6493655</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136622764</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136887471</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99630</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högalund_, Högalund_, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496550</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6493604</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136887471</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136887115</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99662</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högalund_, Högalund_, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496540</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6493678</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136887115</t>
         </is>
       </c>
     </row>
@@ -1146,6 +1864,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99662</v>
+        <v>99668</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99668</v>
+        <v>99670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99670</v>
+        <v>99671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99671</v>
+        <v>99677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99677</v>
+        <v>99681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99681</v>
+        <v>99683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99683</v>
+        <v>99685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99685</v>
+        <v>99698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136621967</v>
       </c>
       <c r="B2" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136626403</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136621778</v>
       </c>
       <c r="B8" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>136622764</v>
       </c>
       <c r="B9" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99698</v>
+        <v>99700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -1660,11 +1660,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högalund_, Högalund_, Ög</t>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99668</v>
+        <v>99671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99700</v>
+        <v>99703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99671</v>
+        <v>99681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99703</v>
+        <v>99713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99681</v>
+        <v>99682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99713</v>
+        <v>99714</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99714</v>
+        <v>99719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99687</v>
+        <v>99690</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99719</v>
+        <v>99722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99722</v>
+        <v>99728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99696</v>
+        <v>99708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99728</v>
+        <v>99740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99708</v>
+        <v>99709</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99740</v>
+        <v>99741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6793-2022 artfynd.xlsx
+++ b/artfynd/A 6793-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136888547</v>
       </c>
       <c r="B4" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136889141</v>
       </c>
       <c r="B5" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136889997</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>136890779</v>
       </c>
       <c r="B7" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>136887471</v>
       </c>
       <c r="B10" t="n">
-        <v>99709</v>
+        <v>99712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136887115</v>
       </c>
       <c r="B11" t="n">
-        <v>99741</v>
+        <v>99744</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
